--- a/teams-and-rosters/CS320-Sp24-Teams.xlsx
+++ b/teams-and-rosters/CS320-Sp24-Teams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\donha\cs320-spring2024\teams-and-rosters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938173FF-1DFE-49EB-80D4-87EF6B7DDB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B83D8D-0E46-45F3-BA9F-5E50CE3AB7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="26264" windowHeight="15127" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3555" yWindow="473" windowWidth="23295" windowHeight="15127" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>In-Class Mentors: Bryce Neptune, Rob Wood</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Spencer Hayes</t>
-  </si>
-  <si>
-    <t>Andrew Loiseau</t>
   </si>
   <si>
     <t>Gabriel Manero</t>
@@ -362,6 +359,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -369,12 +372,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -692,12 +689,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="2:6" ht="25.5" x14ac:dyDescent="0.75">
@@ -708,35 +705,35 @@
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="2:6" ht="21" x14ac:dyDescent="0.65">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="2:6" s="4" customFormat="1" ht="18.399999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="2:6" s="2" customFormat="1" ht="32.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>28</v>
-      </c>
       <c r="E6" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -744,7 +741,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>9</v>
@@ -759,7 +756,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="9"/>
     </row>
@@ -768,16 +765,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="9"/>
     </row>
     <row r="10" spans="2:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
@@ -787,35 +784,35 @@
     </row>
     <row r="11" spans="2:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="2:6" ht="21" x14ac:dyDescent="0.65">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="2:6" s="4" customFormat="1" ht="18.399999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B13" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="B13" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="2:6" ht="32.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="E14" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -824,17 +821,17 @@
         <v>10</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E15" s="14"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="9"/>
       <c r="C16" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="9"/>
     </row>
@@ -844,29 +841,27 @@
         <v>11</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="18"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="18"/>
+        <v>15</v>
+      </c>
+      <c r="E18" s="15"/>
     </row>
     <row r="19" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B19" s="19"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="19"/>
+        <v>17</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
   </sheetData>
